--- a/SumoRanking.xlsx
+++ b/SumoRanking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sauvegarde\Bibliotheque\Informatique\Data\_dataset &amp; pf\Sumo\projetGit_1\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sauvegarde\Bibliotheque\Informatique\Data\_dataset &amp; pf\Sumo\sumo-dashboard1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3936C25C-90AE-4DDF-BF28-6C4D5714B05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853CDBA0-BBD8-49DD-9ED2-31E53BC4D22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{534C3E91-54F2-492F-AA29-565FDAC92146}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15885" xr2:uid="{534C3E91-54F2-492F-AA29-565FDAC92146}"/>
   </bookViews>
   <sheets>
     <sheet name="rank" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="762">
   <si>
     <t>Rank</t>
   </si>
@@ -2319,6 +2319,9 @@
   </si>
   <si>
     <t>États-Unis</t>
+  </si>
+  <si>
+    <t>Sd80 TD</t>
   </si>
 </sst>
 </file>
@@ -2453,8 +2456,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91994C8C-BCCC-434A-8C8A-85E6F99D35EF}" name="Tableau1" displayName="Tableau1" ref="A1:I440" totalsRowShown="0">
-  <autoFilter ref="A1:I440" xr:uid="{91994C8C-BCCC-434A-8C8A-85E6F99D35EF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91994C8C-BCCC-434A-8C8A-85E6F99D35EF}" name="Tableau1" displayName="Tableau1" ref="A1:I441" totalsRowShown="0">
+  <autoFilter ref="A1:I441" xr:uid="{91994C8C-BCCC-434A-8C8A-85E6F99D35EF}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{34264C40-6E55-44DF-B62A-BF85C4E594E2}" name="Rank"/>
     <tableColumn id="2" xr3:uid="{090E0D7F-9102-40E1-A97B-AE2D54E852BA}" name="Rank Name"/>
@@ -2783,7 +2786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1F8E2-6023-4378-812A-146D5510CF4E}">
-  <dimension ref="A1:I440"/>
+  <dimension ref="A1:I441"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -8106,7 +8109,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>215</v>
+        <v>761</v>
       </c>
       <c r="B184" t="s">
         <v>111</v>
@@ -8135,7 +8138,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B185" t="s">
         <v>111</v>
@@ -8164,7 +8167,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B186" t="s">
         <v>111</v>
@@ -8193,7 +8196,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B187" t="s">
         <v>111</v>
@@ -8222,7 +8225,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B188" t="s">
         <v>111</v>
@@ -8251,7 +8254,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B189" t="s">
         <v>111</v>
@@ -8280,7 +8283,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B190" t="s">
         <v>111</v>
@@ -8309,7 +8312,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B191" t="s">
         <v>111</v>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B192" t="s">
         <v>111</v>
@@ -8367,7 +8370,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B193" t="s">
         <v>111</v>
@@ -8396,7 +8399,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B194" t="s">
         <v>111</v>
@@ -8425,7 +8428,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B195" t="s">
         <v>111</v>
@@ -8454,7 +8457,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B196" t="s">
         <v>111</v>
@@ -8483,7 +8486,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B197" t="s">
         <v>111</v>
@@ -8512,7 +8515,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B198" t="s">
         <v>111</v>
@@ -8541,7 +8544,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B199" t="s">
         <v>111</v>
@@ -8570,7 +8573,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B200" t="s">
         <v>111</v>
@@ -8599,7 +8602,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B201" t="s">
         <v>111</v>
@@ -8628,7 +8631,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B202" t="s">
         <v>111</v>
@@ -8657,7 +8660,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="B203" t="s">
         <v>111</v>
@@ -8686,7 +8689,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="B204" t="s">
         <v>111</v>
@@ -8715,7 +8718,7 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B205" t="s">
         <v>111</v>
@@ -8744,7 +8747,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B206" t="s">
         <v>111</v>
@@ -8773,7 +8776,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B207" t="s">
         <v>111</v>
@@ -8802,7 +8805,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B208" t="s">
         <v>111</v>
@@ -8831,25 +8834,25 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="B209" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C209" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D209" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E209" t="s">
         <v>49</v>
       </c>
       <c r="F209" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G209" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H209" t="s">
         <v>50</v>
@@ -8860,7 +8863,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B210" t="s">
         <v>116</v>
@@ -8889,7 +8892,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>239</v>
+        <v>117</v>
       </c>
       <c r="B211" t="s">
         <v>116</v>
@@ -8918,7 +8921,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B212" t="s">
         <v>116</v>
@@ -8947,7 +8950,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B213" t="s">
         <v>116</v>
@@ -8976,7 +8979,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B214" t="s">
         <v>116</v>
@@ -9005,7 +9008,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B215" t="s">
         <v>116</v>
@@ -9034,7 +9037,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B216" t="s">
         <v>116</v>
@@ -9063,7 +9066,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B217" t="s">
         <v>116</v>
@@ -9092,7 +9095,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B218" t="s">
         <v>116</v>
@@ -9121,7 +9124,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B219" t="s">
         <v>116</v>
@@ -9150,7 +9153,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B220" t="s">
         <v>116</v>
@@ -9179,7 +9182,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B221" t="s">
         <v>116</v>
@@ -9208,7 +9211,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B222" t="s">
         <v>116</v>
@@ -9237,7 +9240,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B223" t="s">
         <v>116</v>
@@ -9266,7 +9269,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B224" t="s">
         <v>116</v>
@@ -9295,7 +9298,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B225" t="s">
         <v>116</v>
@@ -9324,7 +9327,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B226" t="s">
         <v>116</v>
@@ -9353,7 +9356,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B227" t="s">
         <v>116</v>
@@ -9382,7 +9385,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B228" t="s">
         <v>116</v>
@@ -9411,7 +9414,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B229" t="s">
         <v>116</v>
@@ -9440,7 +9443,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B230" t="s">
         <v>116</v>
@@ -9469,7 +9472,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B231" t="s">
         <v>116</v>
@@ -9498,7 +9501,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B232" t="s">
         <v>116</v>
@@ -9527,7 +9530,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B233" t="s">
         <v>116</v>
@@ -9556,7 +9559,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B234" t="s">
         <v>116</v>
@@ -9585,7 +9588,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B235" t="s">
         <v>116</v>
@@ -9614,7 +9617,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B236" t="s">
         <v>116</v>
@@ -9643,7 +9646,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B237" t="s">
         <v>116</v>
@@ -9672,7 +9675,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B238" t="s">
         <v>116</v>
@@ -9701,7 +9704,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B239" t="s">
         <v>116</v>
@@ -9730,7 +9733,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B240" t="s">
         <v>116</v>
@@ -9759,7 +9762,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B241" t="s">
         <v>116</v>
@@ -9788,7 +9791,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B242" t="s">
         <v>116</v>
@@ -9817,7 +9820,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B243" t="s">
         <v>116</v>
@@ -9846,7 +9849,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B244" t="s">
         <v>116</v>
@@ -9875,7 +9878,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B245" t="s">
         <v>116</v>
@@ -9904,7 +9907,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B246" t="s">
         <v>116</v>
@@ -9933,7 +9936,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B247" t="s">
         <v>116</v>
@@ -9962,7 +9965,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B248" t="s">
         <v>116</v>
@@ -9991,7 +9994,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B249" t="s">
         <v>116</v>
@@ -10020,7 +10023,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B250" t="s">
         <v>116</v>
@@ -10049,7 +10052,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B251" t="s">
         <v>116</v>
@@ -10078,7 +10081,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B252" t="s">
         <v>116</v>
@@ -10107,7 +10110,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B253" t="s">
         <v>116</v>
@@ -10136,7 +10139,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B254" t="s">
         <v>116</v>
@@ -10165,7 +10168,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B255" t="s">
         <v>116</v>
@@ -10194,7 +10197,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B256" t="s">
         <v>116</v>
@@ -10223,7 +10226,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B257" t="s">
         <v>116</v>
@@ -10252,7 +10255,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B258" t="s">
         <v>116</v>
@@ -10281,7 +10284,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B259" t="s">
         <v>116</v>
@@ -10310,7 +10313,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B260" t="s">
         <v>116</v>
@@ -10339,7 +10342,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B261" t="s">
         <v>116</v>
@@ -10368,7 +10371,7 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B262" t="s">
         <v>116</v>
@@ -10397,7 +10400,7 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B263" t="s">
         <v>116</v>
@@ -10426,7 +10429,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B264" t="s">
         <v>116</v>
@@ -10455,7 +10458,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B265" t="s">
         <v>116</v>
@@ -10484,7 +10487,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B266" t="s">
         <v>116</v>
@@ -10513,7 +10516,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B267" t="s">
         <v>116</v>
@@ -10542,7 +10545,7 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B268" t="s">
         <v>116</v>
@@ -10571,7 +10574,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B269" t="s">
         <v>116</v>
@@ -10600,7 +10603,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B270" t="s">
         <v>116</v>
@@ -10629,7 +10632,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B271" t="s">
         <v>116</v>
@@ -10658,7 +10661,7 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B272" t="s">
         <v>116</v>
@@ -10687,7 +10690,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B273" t="s">
         <v>116</v>
@@ -10716,7 +10719,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B274" t="s">
         <v>116</v>
@@ -10745,7 +10748,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B275" t="s">
         <v>116</v>
@@ -10774,7 +10777,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B276" t="s">
         <v>116</v>
@@ -10803,7 +10806,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B277" t="s">
         <v>116</v>
@@ -10832,7 +10835,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B278" t="s">
         <v>116</v>
@@ -10861,7 +10864,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B279" t="s">
         <v>116</v>
@@ -10890,7 +10893,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B280" t="s">
         <v>116</v>
@@ -10919,7 +10922,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B281" t="s">
         <v>116</v>
@@ -10948,7 +10951,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B282" t="s">
         <v>116</v>
@@ -10977,7 +10980,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B283" t="s">
         <v>116</v>
@@ -11006,7 +11009,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B284" t="s">
         <v>116</v>
@@ -11035,7 +11038,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B285" t="s">
         <v>116</v>
@@ -11064,7 +11067,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B286" t="s">
         <v>116</v>
@@ -11093,7 +11096,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B287" t="s">
         <v>116</v>
@@ -11122,7 +11125,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B288" t="s">
         <v>116</v>
@@ -11151,7 +11154,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B289" t="s">
         <v>116</v>
@@ -11180,7 +11183,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B290" t="s">
         <v>116</v>
@@ -11209,7 +11212,7 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B291" t="s">
         <v>116</v>
@@ -11238,7 +11241,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B292" t="s">
         <v>116</v>
@@ -11267,7 +11270,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B293" t="s">
         <v>116</v>
@@ -11296,7 +11299,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B294" t="s">
         <v>116</v>
@@ -11325,7 +11328,7 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B295" t="s">
         <v>116</v>
@@ -11354,7 +11357,7 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B296" t="s">
         <v>116</v>
@@ -11383,7 +11386,7 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B297" t="s">
         <v>116</v>
@@ -11412,7 +11415,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B298" t="s">
         <v>116</v>
@@ -11441,7 +11444,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B299" t="s">
         <v>116</v>
@@ -11470,7 +11473,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B300" t="s">
         <v>116</v>
@@ -11499,7 +11502,7 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B301" t="s">
         <v>116</v>
@@ -11528,7 +11531,7 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B302" t="s">
         <v>116</v>
@@ -11557,7 +11560,7 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B303" t="s">
         <v>116</v>
@@ -11586,7 +11589,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B304" t="s">
         <v>116</v>
@@ -11615,7 +11618,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B305" t="s">
         <v>116</v>
@@ -11644,7 +11647,7 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B306" t="s">
         <v>116</v>
@@ -11673,7 +11676,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B307" t="s">
         <v>116</v>
@@ -11702,7 +11705,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B308" t="s">
         <v>116</v>
@@ -11731,7 +11734,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B309" t="s">
         <v>116</v>
@@ -11760,7 +11763,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B310" t="s">
         <v>116</v>
@@ -11789,7 +11792,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B311" t="s">
         <v>116</v>
@@ -11818,7 +11821,7 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B312" t="s">
         <v>116</v>
@@ -11847,7 +11850,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B313" t="s">
         <v>116</v>
@@ -11876,7 +11879,7 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B314" t="s">
         <v>116</v>
@@ -11905,7 +11908,7 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B315" t="s">
         <v>116</v>
@@ -11934,7 +11937,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B316" t="s">
         <v>116</v>
@@ -11963,7 +11966,7 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B317" t="s">
         <v>116</v>
@@ -11992,7 +11995,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B318" t="s">
         <v>116</v>
@@ -12021,7 +12024,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B319" t="s">
         <v>116</v>
@@ -12050,7 +12053,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B320" t="s">
         <v>116</v>
@@ -12079,7 +12082,7 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B321" t="s">
         <v>116</v>
@@ -12108,7 +12111,7 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B322" t="s">
         <v>116</v>
@@ -12137,7 +12140,7 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B323" t="s">
         <v>116</v>
@@ -12166,7 +12169,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B324" t="s">
         <v>116</v>
@@ -12195,7 +12198,7 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B325" t="s">
         <v>116</v>
@@ -12224,7 +12227,7 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B326" t="s">
         <v>116</v>
@@ -12253,7 +12256,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B327" t="s">
         <v>116</v>
@@ -12282,7 +12285,7 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B328" t="s">
         <v>116</v>
@@ -12311,7 +12314,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B329" t="s">
         <v>116</v>
@@ -12340,7 +12343,7 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B330" t="s">
         <v>116</v>
@@ -12369,7 +12372,7 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B331" t="s">
         <v>116</v>
@@ -12398,7 +12401,7 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B332" t="s">
         <v>116</v>
@@ -12427,7 +12430,7 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B333" t="s">
         <v>116</v>
@@ -12456,7 +12459,7 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>446</v>
+        <v>361</v>
       </c>
       <c r="B334" t="s">
         <v>116</v>
@@ -12485,7 +12488,7 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B335" t="s">
         <v>116</v>
@@ -12514,7 +12517,7 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B336" t="s">
         <v>116</v>
@@ -12543,7 +12546,7 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B337" t="s">
         <v>116</v>
@@ -12572,7 +12575,7 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>118</v>
+        <v>449</v>
       </c>
       <c r="B338" t="s">
         <v>116</v>
@@ -12601,7 +12604,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>450</v>
+        <v>118</v>
       </c>
       <c r="B339" t="s">
         <v>116</v>
@@ -12630,7 +12633,7 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B340" t="s">
         <v>116</v>
@@ -12659,7 +12662,7 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B341" t="s">
         <v>116</v>
@@ -12688,7 +12691,7 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B342" t="s">
         <v>116</v>
@@ -12717,7 +12720,7 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B343" t="s">
         <v>116</v>
@@ -12746,7 +12749,7 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B344" t="s">
         <v>116</v>
@@ -12775,7 +12778,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B345" t="s">
         <v>116</v>
@@ -12804,7 +12807,7 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B346" t="s">
         <v>116</v>
@@ -12833,7 +12836,7 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B347" t="s">
         <v>116</v>
@@ -12862,7 +12865,7 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B348" t="s">
         <v>116</v>
@@ -12891,7 +12894,7 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="B349" t="s">
         <v>116</v>
@@ -12920,7 +12923,7 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B350" t="s">
         <v>116</v>
@@ -12949,7 +12952,7 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B351" t="s">
         <v>116</v>
@@ -12978,7 +12981,7 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B352" t="s">
         <v>116</v>
@@ -13007,7 +13010,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B353" t="s">
         <v>116</v>
@@ -13036,7 +13039,7 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B354" t="s">
         <v>116</v>
@@ -13065,7 +13068,7 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B355" t="s">
         <v>116</v>
@@ -13094,7 +13097,7 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B356" t="s">
         <v>116</v>
@@ -13123,7 +13126,7 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B357" t="s">
         <v>116</v>
@@ -13152,7 +13155,7 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B358" t="s">
         <v>116</v>
@@ -13181,25 +13184,25 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>119</v>
+        <v>467</v>
       </c>
       <c r="B359" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C359" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D359" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E359" t="s">
         <v>49</v>
       </c>
       <c r="F359" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G359" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H359" t="s">
         <v>50</v>
@@ -13210,7 +13213,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B360" t="s">
         <v>120</v>
@@ -13239,7 +13242,7 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>362</v>
+        <v>121</v>
       </c>
       <c r="B361" t="s">
         <v>120</v>
@@ -13268,7 +13271,7 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B362" t="s">
         <v>120</v>
@@ -13297,7 +13300,7 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B363" t="s">
         <v>120</v>
@@ -13326,7 +13329,7 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B364" t="s">
         <v>120</v>
@@ -13355,7 +13358,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B365" t="s">
         <v>120</v>
@@ -13384,7 +13387,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B366" t="s">
         <v>120</v>
@@ -13413,7 +13416,7 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B367" t="s">
         <v>120</v>
@@ -13442,7 +13445,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B368" t="s">
         <v>120</v>
@@ -13471,7 +13474,7 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B369" t="s">
         <v>120</v>
@@ -13500,7 +13503,7 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B370" t="s">
         <v>120</v>
@@ -13529,7 +13532,7 @@
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B371" t="s">
         <v>120</v>
@@ -13558,7 +13561,7 @@
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B372" t="s">
         <v>120</v>
@@ -13587,7 +13590,7 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B373" t="s">
         <v>120</v>
@@ -13616,7 +13619,7 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B374" t="s">
         <v>120</v>
@@ -13645,7 +13648,7 @@
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B375" t="s">
         <v>120</v>
@@ -13674,7 +13677,7 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B376" t="s">
         <v>120</v>
@@ -13703,7 +13706,7 @@
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B377" t="s">
         <v>120</v>
@@ -13732,7 +13735,7 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B378" t="s">
         <v>120</v>
@@ -13761,7 +13764,7 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B379" t="s">
         <v>120</v>
@@ -13790,7 +13793,7 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B380" t="s">
         <v>120</v>
@@ -13819,7 +13822,7 @@
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B381" t="s">
         <v>120</v>
@@ -13848,7 +13851,7 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B382" t="s">
         <v>120</v>
@@ -13877,7 +13880,7 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B383" t="s">
         <v>120</v>
@@ -13906,7 +13909,7 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B384" t="s">
         <v>120</v>
@@ -13935,7 +13938,7 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B385" t="s">
         <v>120</v>
@@ -13964,7 +13967,7 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B386" t="s">
         <v>120</v>
@@ -13993,7 +13996,7 @@
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B387" t="s">
         <v>120</v>
@@ -14022,7 +14025,7 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B388" t="s">
         <v>120</v>
@@ -14051,7 +14054,7 @@
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B389" t="s">
         <v>120</v>
@@ -14080,7 +14083,7 @@
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B390" t="s">
         <v>120</v>
@@ -14109,7 +14112,7 @@
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B391" t="s">
         <v>120</v>
@@ -14138,7 +14141,7 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B392" t="s">
         <v>120</v>
@@ -14167,7 +14170,7 @@
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B393" t="s">
         <v>120</v>
@@ -14196,7 +14199,7 @@
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B394" t="s">
         <v>120</v>
@@ -14225,7 +14228,7 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B395" t="s">
         <v>120</v>
@@ -14254,7 +14257,7 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B396" t="s">
         <v>120</v>
@@ -14283,7 +14286,7 @@
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B397" t="s">
         <v>120</v>
@@ -14312,7 +14315,7 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B398" t="s">
         <v>120</v>
@@ -14341,7 +14344,7 @@
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B399" t="s">
         <v>120</v>
@@ -14370,7 +14373,7 @@
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B400" t="s">
         <v>120</v>
@@ -14399,7 +14402,7 @@
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B401" t="s">
         <v>120</v>
@@ -14428,7 +14431,7 @@
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B402" t="s">
         <v>120</v>
@@ -14457,7 +14460,7 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B403" t="s">
         <v>120</v>
@@ -14486,7 +14489,7 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B404" t="s">
         <v>120</v>
@@ -14515,7 +14518,7 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B405" t="s">
         <v>120</v>
@@ -14544,7 +14547,7 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B406" t="s">
         <v>120</v>
@@ -14573,7 +14576,7 @@
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B407" t="s">
         <v>120</v>
@@ -14602,7 +14605,7 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B408" t="s">
         <v>120</v>
@@ -14631,7 +14634,7 @@
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B409" t="s">
         <v>120</v>
@@ -14660,7 +14663,7 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B410" t="s">
         <v>120</v>
@@ -14689,7 +14692,7 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B411" t="s">
         <v>120</v>
@@ -14718,7 +14721,7 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B412" t="s">
         <v>120</v>
@@ -14747,7 +14750,7 @@
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B413" t="s">
         <v>120</v>
@@ -14776,7 +14779,7 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B414" t="s">
         <v>120</v>
@@ -14805,7 +14808,7 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B415" t="s">
         <v>120</v>
@@ -14834,7 +14837,7 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B416" t="s">
         <v>120</v>
@@ -14863,7 +14866,7 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B417" t="s">
         <v>120</v>
@@ -14892,7 +14895,7 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B418" t="s">
         <v>120</v>
@@ -14921,7 +14924,7 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B419" t="s">
         <v>120</v>
@@ -14950,7 +14953,7 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B420" t="s">
         <v>120</v>
@@ -14979,7 +14982,7 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B421" t="s">
         <v>120</v>
@@ -15008,7 +15011,7 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B422" t="s">
         <v>120</v>
@@ -15037,7 +15040,7 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B423" t="s">
         <v>120</v>
@@ -15066,7 +15069,7 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B424" t="s">
         <v>120</v>
@@ -15095,7 +15098,7 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B425" t="s">
         <v>120</v>
@@ -15124,7 +15127,7 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B426" t="s">
         <v>120</v>
@@ -15153,7 +15156,7 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B427" t="s">
         <v>120</v>
@@ -15182,7 +15185,7 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B428" t="s">
         <v>120</v>
@@ -15211,7 +15214,7 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B429" t="s">
         <v>120</v>
@@ -15240,7 +15243,7 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B430" t="s">
         <v>120</v>
@@ -15269,7 +15272,7 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B431" t="s">
         <v>120</v>
@@ -15298,7 +15301,7 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B432" t="s">
         <v>120</v>
@@ -15327,7 +15330,7 @@
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B433" t="s">
         <v>120</v>
@@ -15356,7 +15359,7 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B434" t="s">
         <v>120</v>
@@ -15385,7 +15388,7 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B435" t="s">
         <v>120</v>
@@ -15414,7 +15417,7 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B436" t="s">
         <v>120</v>
@@ -15443,7 +15446,7 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B437" t="s">
         <v>120</v>
@@ -15472,7 +15475,7 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B438" t="s">
         <v>120</v>
@@ -15501,28 +15504,28 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>122</v>
+        <v>439</v>
       </c>
       <c r="B439" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C439" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D439" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E439" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="F439" s="1">
         <v>6</v>
       </c>
       <c r="G439" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H439" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I439" s="1">
         <v>438</v>
@@ -15530,16 +15533,16 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B440" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C440" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D440" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E440" t="s">
         <v>124</v>
@@ -15548,13 +15551,42 @@
         <v>6</v>
       </c>
       <c r="G440" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H440" t="s">
         <v>125</v>
       </c>
       <c r="I440" s="1">
         <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>126</v>
+      </c>
+      <c r="B441" t="s">
+        <v>127</v>
+      </c>
+      <c r="C441" t="s">
+        <v>127</v>
+      </c>
+      <c r="D441" t="s">
+        <v>127</v>
+      </c>
+      <c r="E441" t="s">
+        <v>124</v>
+      </c>
+      <c r="F441" s="1">
+        <v>6</v>
+      </c>
+      <c r="G441" s="1">
+        <v>12</v>
+      </c>
+      <c r="H441" t="s">
+        <v>125</v>
+      </c>
+      <c r="I441" s="1">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
